--- a/AgenticAI/TechAcademy_GenAI_agenticAL_Proposed_ToC.xlsx
+++ b/AgenticAI/TechAcademy_GenAI_agenticAL_Proposed_ToC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CB8890-E654-40A4-BF68-329D28C056A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4A0845-B166-400D-8EAB-58100D7E75B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="25830" windowHeight="14160" xr2:uid="{76794B29-AF1B-488B-A803-5D384C927E03}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="94">
   <si>
     <t>Pre- Requisites</t>
   </si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>done with BaseModel class</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1418,7 @@
       </c>
       <c r="F34" s="23"/>
       <c r="G34" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1425,7 +1431,7 @@
       </c>
       <c r="F35" s="23"/>
       <c r="G35" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1529,6 +1535,9 @@
         <v>48</v>
       </c>
       <c r="F43" s="23"/>
+      <c r="G43" s="7" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
@@ -1539,6 +1548,9 @@
         <v>49</v>
       </c>
       <c r="F44" s="23"/>
+      <c r="G44" s="7" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
@@ -1613,6 +1625,9 @@
         <v>53</v>
       </c>
       <c r="F49" s="23"/>
+      <c r="G49" s="7" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="50"/>
@@ -1625,6 +1640,9 @@
         <v>50</v>
       </c>
       <c r="F50" s="23"/>
+      <c r="G50" s="7" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="50"/>
@@ -1675,6 +1693,9 @@
         <v>71</v>
       </c>
       <c r="F53" s="25"/>
+      <c r="G53" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="50"/>

--- a/AgenticAI/TechAcademy_GenAI_agenticAL_Proposed_ToC.xlsx
+++ b/AgenticAI/TechAcademy_GenAI_agenticAL_Proposed_ToC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\tut_youtube\AgenticAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4A0845-B166-400D-8EAB-58100D7E75B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EA5912-5C56-4A68-91DE-10C21992511D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25830" windowHeight="14160" xr2:uid="{76794B29-AF1B-488B-A803-5D384C927E03}"/>
+    <workbookView xWindow="2490" yWindow="1320" windowWidth="25830" windowHeight="14160" xr2:uid="{76794B29-AF1B-488B-A803-5D384C927E03}"/>
   </bookViews>
   <sheets>
     <sheet name="agenda" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="94">
   <si>
     <t>Pre- Requisites</t>
   </si>
@@ -606,6 +606,36 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -615,14 +645,17 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -632,39 +665,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1013,13 +1013,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
       <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1027,11 +1027,11 @@
       <c r="B2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1054,16 +1054,16 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="39">
         <v>0.5</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="49" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -1072,42 +1072,42 @@
       <c r="F5" s="23"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="39"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="50"/>
       <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="39"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="50"/>
       <c r="E7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="40"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="4" t="s">
         <v>72</v>
       </c>
       <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="35">
+      <c r="A9" s="37"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="39">
         <v>3</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="49" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -1116,38 +1116,38 @@
       <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6" ht="27" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="39"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="50"/>
       <c r="E10" s="4" t="s">
         <v>56</v>
       </c>
       <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="50"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="39"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="50"/>
       <c r="E11" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="39"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="50"/>
       <c r="E12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="50"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="3">
         <v>0.5</v>
       </c>
@@ -1160,14 +1160,14 @@
       <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50"/>
-      <c r="B14" s="35" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="39">
         <v>1</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="42" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -1176,32 +1176,32 @@
       <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="33"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="43"/>
       <c r="E15" s="4" t="s">
         <v>74</v>
       </c>
       <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="34"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="44"/>
       <c r="E16" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="35">
+      <c r="A17" s="37"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="39">
         <v>2</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="49" t="s">
         <v>62</v>
       </c>
       <c r="E17" s="14" t="s">
@@ -1210,48 +1210,48 @@
       <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="50"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="39"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="50"/>
       <c r="E18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="39"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="50"/>
       <c r="E19" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="39"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="50"/>
       <c r="E20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F20" s="23"/>
     </row>
     <row r="21" spans="1:7" ht="27" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="39"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="50"/>
       <c r="E21" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F21" s="23"/>
     </row>
     <row r="22" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
-      <c r="B22" s="36"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="41"/>
       <c r="C22" s="3">
         <v>1</v>
       </c>
@@ -1264,16 +1264,16 @@
       <c r="F22" s="23"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="39">
         <v>2</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="49" t="s">
         <v>17</v>
       </c>
       <c r="E23" s="4" t="s">
@@ -1282,10 +1282,10 @@
       <c r="F23" s="24"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="39"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="50"/>
       <c r="E24" s="4" t="s">
         <v>59</v>
       </c>
@@ -1295,28 +1295,28 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="39"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="50"/>
       <c r="E25" s="4" t="s">
         <v>63</v>
       </c>
       <c r="F25" s="24"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="50"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="39"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="50"/>
       <c r="E26" s="17" t="s">
         <v>65</v>
       </c>
       <c r="F26" s="24"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="50"/>
-      <c r="B27" s="44"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="48"/>
       <c r="C27" s="3">
         <v>1</v>
       </c>
@@ -1329,56 +1329,56 @@
       <c r="F27" s="24"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="35">
+      <c r="A28" s="37"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="39">
         <v>1</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="49" t="s">
         <v>66</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="45" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="39"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="50"/>
       <c r="E29" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="42"/>
+      <c r="F29" s="46"/>
       <c r="G29" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="50"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="40"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="43"/>
+      <c r="F30" s="47"/>
       <c r="G30" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="50"/>
-      <c r="B31" s="45" t="s">
+      <c r="A31" s="37"/>
+      <c r="B31" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="39">
         <v>3</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="42" t="s">
         <v>67</v>
       </c>
       <c r="E31" s="4" t="s">
@@ -1387,10 +1387,10 @@
       <c r="F31" s="23"/>
     </row>
     <row r="32" spans="1:7" ht="27" x14ac:dyDescent="0.25">
-      <c r="A32" s="50"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="33"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="43"/>
       <c r="E32" s="29" t="s">
         <v>60</v>
       </c>
@@ -1399,20 +1399,20 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="50"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="33"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="43"/>
       <c r="E33" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F33" s="23"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="50"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="33"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="43"/>
       <c r="E34" s="4" t="s">
         <v>28</v>
       </c>
@@ -1422,10 +1422,10 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="50"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="34"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="44"/>
       <c r="E35" s="4" t="s">
         <v>29</v>
       </c>
@@ -1435,8 +1435,8 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="51"/>
-      <c r="B36" s="45"/>
+      <c r="A36" s="38"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="12">
         <v>1</v>
       </c>
@@ -1449,16 +1449,16 @@
       <c r="F36" s="23"/>
     </row>
     <row r="37" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="45" t="s">
+      <c r="B37" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="35">
+      <c r="C37" s="39">
         <v>3</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="42" t="s">
         <v>30</v>
       </c>
       <c r="E37" s="5" t="s">
@@ -1467,28 +1467,28 @@
       <c r="F37" s="23"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="50"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="33"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="43"/>
       <c r="E38" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F38" s="23"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="50"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="34"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="44"/>
       <c r="E39" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F39" s="23"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
-      <c r="B40" s="45"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="3">
         <v>1</v>
       </c>
@@ -1501,14 +1501,14 @@
       <c r="F40" s="23"/>
     </row>
     <row r="41" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
-      <c r="B41" s="45" t="s">
+      <c r="A41" s="37"/>
+      <c r="B41" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="39">
         <v>2</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="42" t="s">
         <v>35</v>
       </c>
       <c r="E41" s="20" t="s">
@@ -1517,20 +1517,20 @@
       <c r="F41" s="23"/>
     </row>
     <row r="42" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="50"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="33"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="43"/>
       <c r="E42" s="20" t="s">
         <v>47</v>
       </c>
       <c r="F42" s="23"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="50"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="33"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="43"/>
       <c r="E43" s="20" t="s">
         <v>48</v>
       </c>
@@ -1540,10 +1540,10 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="34"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="44"/>
       <c r="E44" s="20" t="s">
         <v>49</v>
       </c>
@@ -1553,8 +1553,8 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
-      <c r="B45" s="45"/>
+      <c r="A45" s="37"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="10">
         <v>0.5</v>
       </c>
@@ -1567,8 +1567,8 @@
       <c r="F45" s="23"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="50"/>
-      <c r="B46" s="45"/>
+      <c r="A46" s="37"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="3">
         <v>1</v>
       </c>
@@ -1579,10 +1579,13 @@
         <v>81</v>
       </c>
       <c r="F46" s="23"/>
+      <c r="G46" s="7" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="51"/>
-      <c r="B47" s="45"/>
+      <c r="A47" s="38"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="11">
         <v>0.5</v>
       </c>
@@ -1595,10 +1598,10 @@
       <c r="F47" s="23"/>
     </row>
     <row r="48" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="11">
@@ -1613,9 +1616,9 @@
       <c r="F48" s="23"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
-      <c r="B49" s="37"/>
-      <c r="C49" s="35">
+      <c r="A49" s="37"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="39">
         <v>1.5</v>
       </c>
       <c r="D49" s="6" t="s">
@@ -1630,9 +1633,9 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="50"/>
-      <c r="B50" s="37"/>
-      <c r="C50" s="36"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="41"/>
       <c r="D50" s="6" t="s">
         <v>37</v>
       </c>
@@ -1645,8 +1648,8 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="50"/>
-      <c r="B51" s="37"/>
+      <c r="A51" s="37"/>
+      <c r="B51" s="40"/>
       <c r="C51" s="3">
         <v>1</v>
       </c>
@@ -1662,8 +1665,8 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
-      <c r="B52" s="36"/>
+      <c r="A52" s="37"/>
+      <c r="B52" s="41"/>
       <c r="C52" s="3">
         <v>0.5</v>
       </c>
@@ -1679,8 +1682,8 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="50"/>
-      <c r="B53" s="45" t="s">
+      <c r="A53" s="37"/>
+      <c r="B53" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="3">
@@ -1698,8 +1701,8 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="50"/>
-      <c r="B54" s="45"/>
+      <c r="A54" s="37"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="3">
         <v>1</v>
       </c>
@@ -1712,8 +1715,8 @@
       <c r="F54" s="25"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="51"/>
-      <c r="B55" s="45"/>
+      <c r="A55" s="38"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="3">
         <v>1.5</v>
       </c>
@@ -1726,7 +1729,7 @@
       <c r="F55" s="25"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="48" t="s">
+      <c r="A56" s="34" t="s">
         <v>41</v>
       </c>
       <c r="B56" s="13" t="s">
@@ -1746,7 +1749,7 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="48"/>
+      <c r="A57" s="34"/>
       <c r="B57" s="13" t="s">
         <v>11</v>
       </c>
@@ -1786,6 +1789,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="D41:D44"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="D31:D35"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:D12"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A56:A57"/>
@@ -1802,25 +1824,6 @@
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="D37:D39"/>
     <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="D31:D35"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="D41:D44"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
